--- a/FES03N.xlsx
+++ b/FES03N.xlsx
@@ -1,34 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{E6BDD824-8285-D34A-AE81-4405D0222D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="285">
   <si>
     <t/>
   </si>
@@ -883,46 +866,19 @@
   </si>
   <si>
     <t>106</t>
-  </si>
-  <si>
-    <t>KURMA DATE CROWN PCS</t>
-  </si>
-  <si>
-    <t>FES04N</t>
-  </si>
-  <si>
-    <t>PT,(E-2H)</t>
-  </si>
-  <si>
-    <t>KURMA DATE CROWN 250</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>KRM TUNISIA HIJRA500</t>
-  </si>
-  <si>
-    <t>KURMA TUNIS BRARI500</t>
-  </si>
-  <si>
-    <t>KURMA MEDJOOL  PCK</t>
-  </si>
-  <si>
-    <t>KURMA SAYER BRARI250</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -943,16 +899,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1301,19 +1257,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F93"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="9.953125" customWidth="1"/>
-    <col min="2" max="2" width="22.05859375" customWidth="1"/>
-    <col min="3" max="3" width="7.93359375" customWidth="1"/>
-    <col min="4" max="4" width="2.95703125" customWidth="1"/>
-    <col min="5" max="5" width="4.9765625" customWidth="1"/>
-    <col min="6" max="6" width="13.046875" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="5" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1333,7 +1289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1353,7 +1309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1373,7 +1329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1393,7 +1349,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1413,7 +1369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1433,7 +1389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -1453,7 +1409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1473,7 +1429,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -1493,7 +1449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -1513,7 +1469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -1533,7 +1489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -1553,7 +1509,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>37</v>
       </c>
@@ -1573,7 +1529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
@@ -1593,7 +1549,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>44</v>
       </c>
@@ -1613,7 +1569,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>47</v>
       </c>
@@ -1633,7 +1589,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>50</v>
       </c>
@@ -1653,7 +1609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>53</v>
       </c>
@@ -1673,7 +1629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>56</v>
       </c>
@@ -1693,7 +1649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>59</v>
       </c>
@@ -1713,7 +1669,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>63</v>
       </c>
@@ -1733,7 +1689,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>66</v>
       </c>
@@ -1753,7 +1709,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>69</v>
       </c>
@@ -1773,7 +1729,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>72</v>
       </c>
@@ -1793,7 +1749,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>76</v>
       </c>
@@ -1813,7 +1769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>79</v>
       </c>
@@ -1833,7 +1789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>82</v>
       </c>
@@ -1853,7 +1809,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>85</v>
       </c>
@@ -1873,7 +1829,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>88</v>
       </c>
@@ -1893,7 +1849,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>91</v>
       </c>
@@ -1913,7 +1869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>94</v>
       </c>
@@ -1933,7 +1889,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>97</v>
       </c>
@@ -1953,7 +1909,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>100</v>
       </c>
@@ -1973,7 +1929,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>104</v>
       </c>
@@ -1993,7 +1949,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>107</v>
       </c>
@@ -2013,7 +1969,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>110</v>
       </c>
@@ -2033,7 +1989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>113</v>
       </c>
@@ -2053,7 +2009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>116</v>
       </c>
@@ -2073,7 +2029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>119</v>
       </c>
@@ -2093,7 +2049,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>122</v>
       </c>
@@ -2113,7 +2069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>125</v>
       </c>
@@ -2133,7 +2089,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>129</v>
       </c>
@@ -2153,7 +2109,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>132</v>
       </c>
@@ -2173,7 +2129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>135</v>
       </c>
@@ -2193,7 +2149,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>138</v>
       </c>
@@ -2213,7 +2169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>141</v>
       </c>
@@ -2233,7 +2189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>144</v>
       </c>
@@ -2253,7 +2209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>147</v>
       </c>
@@ -2273,7 +2229,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>150</v>
       </c>
@@ -2293,7 +2249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>153</v>
       </c>
@@ -2313,7 +2269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>156</v>
       </c>
@@ -2333,7 +2289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>159</v>
       </c>
@@ -2353,7 +2309,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>162</v>
       </c>
@@ -2373,7 +2329,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>165</v>
       </c>
@@ -2393,7 +2349,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>168</v>
       </c>
@@ -2413,7 +2369,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>171</v>
       </c>
@@ -2433,7 +2389,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>174</v>
       </c>
@@ -2453,7 +2409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>177</v>
       </c>
@@ -2473,7 +2429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>180</v>
       </c>
@@ -2493,7 +2449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>183</v>
       </c>
@@ -2513,7 +2469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>186</v>
       </c>
@@ -2533,7 +2489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>189</v>
       </c>
@@ -2553,7 +2509,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>192</v>
       </c>
@@ -2573,7 +2529,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>195</v>
       </c>
@@ -2593,7 +2549,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>198</v>
       </c>
@@ -2613,7 +2569,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>201</v>
       </c>
@@ -2633,7 +2589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>204</v>
       </c>
@@ -2653,7 +2609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>207</v>
       </c>
@@ -2673,7 +2629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>210</v>
       </c>
@@ -2693,7 +2649,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>213</v>
       </c>
@@ -2713,7 +2669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>216</v>
       </c>
@@ -2733,7 +2689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>219</v>
       </c>
@@ -2753,7 +2709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>222</v>
       </c>
@@ -2773,7 +2729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>225</v>
       </c>
@@ -2793,7 +2749,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>228</v>
       </c>
@@ -2813,7 +2769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>231</v>
       </c>
@@ -2833,7 +2789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>234</v>
       </c>
@@ -2853,7 +2809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>237</v>
       </c>
@@ -2873,7 +2829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>240</v>
       </c>
@@ -2893,7 +2849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>243</v>
       </c>
@@ -2913,7 +2869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>246</v>
       </c>
@@ -2933,7 +2889,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>249</v>
       </c>
@@ -2953,7 +2909,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>252</v>
       </c>
@@ -2973,7 +2929,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>255</v>
       </c>
@@ -2993,7 +2949,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>258</v>
       </c>
@@ -3013,7 +2969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>261</v>
       </c>
@@ -3033,7 +2989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>264</v>
       </c>
@@ -3053,7 +3009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>267</v>
       </c>
@@ -3073,7 +3029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>270</v>
       </c>
@@ -3093,7 +3049,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>273</v>
       </c>
@@ -3113,7 +3069,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>276</v>
       </c>
@@ -3133,7 +3089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>279</v>
       </c>
@@ -3153,7 +3109,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>282</v>
       </c>
@@ -3173,128 +3129,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A95">
-        <v>20070380</v>
-      </c>
-      <c r="B95" t="s">
-        <v>285</v>
-      </c>
-      <c r="C95" t="s">
-        <v>286</v>
-      </c>
-      <c r="D95">
-        <v>1</v>
-      </c>
-      <c r="E95">
-        <v>1</v>
-      </c>
-      <c r="F95" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A96">
-        <v>20046368</v>
-      </c>
-      <c r="B96" t="s">
-        <v>288</v>
-      </c>
-      <c r="C96" t="s">
-        <v>286</v>
-      </c>
-      <c r="D96">
-        <v>1</v>
-      </c>
-      <c r="E96">
-        <v>2</v>
-      </c>
-      <c r="F96" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A97">
-        <v>20016388</v>
-      </c>
-      <c r="B97" t="s">
-        <v>290</v>
-      </c>
-      <c r="C97" t="s">
-        <v>286</v>
-      </c>
-      <c r="D97">
-        <v>1</v>
-      </c>
-      <c r="E97">
-        <v>3</v>
-      </c>
-      <c r="F97" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98">
-        <v>20140218</v>
-      </c>
-      <c r="B98" t="s">
-        <v>291</v>
-      </c>
-      <c r="C98" t="s">
-        <v>286</v>
-      </c>
-      <c r="D98">
-        <v>1</v>
-      </c>
-      <c r="E98">
-        <v>4</v>
-      </c>
-      <c r="F98" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99">
-        <v>20113971</v>
-      </c>
-      <c r="B99" t="s">
-        <v>292</v>
-      </c>
-      <c r="C99" t="s">
-        <v>286</v>
-      </c>
-      <c r="D99">
-        <v>1</v>
-      </c>
-      <c r="E99">
-        <v>5</v>
-      </c>
-      <c r="F99" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A100">
-        <v>20140192</v>
-      </c>
-      <c r="B100" t="s">
-        <v>293</v>
-      </c>
-      <c r="C100" t="s">
-        <v>286</v>
-      </c>
-      <c r="D100">
-        <v>1</v>
-      </c>
-      <c r="E100">
-        <v>6</v>
-      </c>
-      <c r="F100" t="s">
-        <v>287</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>